--- a/data/nzd0129/nzd0129.xlsx
+++ b/data/nzd0129/nzd0129.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J639"/>
+  <dimension ref="A1:J643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23412,7 +23412,7 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>335.16</v>
+        <v>334.59</v>
       </c>
       <c r="C639" t="n">
         <v>343.14</v>
@@ -23436,6 +23436,150 @@
         <v>367.91</v>
       </c>
       <c r="J639" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>331.99</v>
+      </c>
+      <c r="C640" t="n">
+        <v>341.53</v>
+      </c>
+      <c r="D640" t="n">
+        <v>345.59</v>
+      </c>
+      <c r="E640" t="n">
+        <v>347.09</v>
+      </c>
+      <c r="F640" t="n">
+        <v>359.64</v>
+      </c>
+      <c r="G640" t="n">
+        <v>365.16</v>
+      </c>
+      <c r="H640" t="n">
+        <v>366.81</v>
+      </c>
+      <c r="I640" t="n">
+        <v>367.95</v>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>326.66</v>
+      </c>
+      <c r="C641" t="n">
+        <v>341.62</v>
+      </c>
+      <c r="D641" t="n">
+        <v>346.57</v>
+      </c>
+      <c r="E641" t="n">
+        <v>347.18</v>
+      </c>
+      <c r="F641" t="n">
+        <v>359.57</v>
+      </c>
+      <c r="G641" t="n">
+        <v>364.58</v>
+      </c>
+      <c r="H641" t="n">
+        <v>367.04</v>
+      </c>
+      <c r="I641" t="n">
+        <v>367.9</v>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>326.66</v>
+      </c>
+      <c r="C642" t="n">
+        <v>341.95</v>
+      </c>
+      <c r="D642" t="n">
+        <v>346.09</v>
+      </c>
+      <c r="E642" t="n">
+        <v>346.68</v>
+      </c>
+      <c r="F642" t="n">
+        <v>358.51</v>
+      </c>
+      <c r="G642" t="n">
+        <v>363.23</v>
+      </c>
+      <c r="H642" t="n">
+        <v>366.19</v>
+      </c>
+      <c r="I642" t="n">
+        <v>367.9</v>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>324.84</v>
+      </c>
+      <c r="C643" t="n">
+        <v>341.08</v>
+      </c>
+      <c r="D643" t="n">
+        <v>345.49</v>
+      </c>
+      <c r="E643" t="n">
+        <v>346.84</v>
+      </c>
+      <c r="F643" t="n">
+        <v>359.18</v>
+      </c>
+      <c r="G643" t="n">
+        <v>363.63</v>
+      </c>
+      <c r="H643" t="n">
+        <v>366.56</v>
+      </c>
+      <c r="I643" t="n">
+        <v>368.32</v>
+      </c>
+      <c r="J643" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23452,7 +23596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B651"/>
+  <dimension ref="A1:B655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29965,6 +30109,46 @@
       </c>
       <c r="B651" t="n">
         <v>1.04</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="n">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -30133,28 +30317,28 @@
         <v>0.059</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2710414979637037</v>
+        <v>-0.2927933749273703</v>
       </c>
       <c r="J2" t="n">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="K2" t="n">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02854128251049948</v>
+        <v>0.03315631136190123</v>
       </c>
       <c r="M2" t="n">
-        <v>10.35019659727885</v>
+        <v>10.40272735325131</v>
       </c>
       <c r="N2" t="n">
-        <v>139.1525966241944</v>
+        <v>140.1949020948929</v>
       </c>
       <c r="O2" t="n">
-        <v>11.79629588575136</v>
+        <v>11.84039281843694</v>
       </c>
       <c r="P2" t="n">
-        <v>352.1936665402262</v>
+        <v>352.4267959557174</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30211,28 +30395,28 @@
         <v>0.0418</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3866979734326655</v>
+        <v>-0.3936199376762383</v>
       </c>
       <c r="J3" t="n">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="K3" t="n">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1389343383562653</v>
+        <v>0.144501661037819</v>
       </c>
       <c r="M3" t="n">
-        <v>6.06683340090451</v>
+        <v>6.068891830517907</v>
       </c>
       <c r="N3" t="n">
-        <v>51.44085164595166</v>
+        <v>51.31033680225099</v>
       </c>
       <c r="O3" t="n">
-        <v>7.172227802151272</v>
+        <v>7.163123397111835</v>
       </c>
       <c r="P3" t="n">
-        <v>357.5122332345733</v>
+        <v>357.5864670630987</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30289,28 +30473,28 @@
         <v>0.0655</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1571837983119384</v>
+        <v>-0.1640083304711157</v>
       </c>
       <c r="J4" t="n">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="K4" t="n">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06579013787203336</v>
+        <v>0.07150680558206102</v>
       </c>
       <c r="M4" t="n">
-        <v>3.351524084890551</v>
+        <v>3.364878627948316</v>
       </c>
       <c r="N4" t="n">
-        <v>19.47318071775074</v>
+        <v>19.53743384835627</v>
       </c>
       <c r="O4" t="n">
-        <v>4.412842702584213</v>
+        <v>4.420116949624328</v>
       </c>
       <c r="P4" t="n">
-        <v>355.6554849809159</v>
+        <v>355.7286729560913</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30367,28 +30551,28 @@
         <v>0.061</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2974065026861988</v>
+        <v>-0.3025526375742647</v>
       </c>
       <c r="J5" t="n">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="K5" t="n">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2548510896855261</v>
+        <v>0.2627124357098071</v>
       </c>
       <c r="M5" t="n">
-        <v>2.817511661295284</v>
+        <v>2.824367913248808</v>
       </c>
       <c r="N5" t="n">
-        <v>14.33619588565415</v>
+        <v>14.35189322577166</v>
       </c>
       <c r="O5" t="n">
-        <v>3.786316928844461</v>
+        <v>3.788389265343737</v>
       </c>
       <c r="P5" t="n">
-        <v>359.0853426255493</v>
+        <v>359.1405497263555</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30445,28 +30629,28 @@
         <v>0.0892</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0005519284697417486</v>
+        <v>-0.006974324035298916</v>
       </c>
       <c r="J6" t="n">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="K6" t="n">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="L6" t="n">
-        <v>1.801198265205528e-06</v>
+        <v>0.0002846989093194807</v>
       </c>
       <c r="M6" t="n">
-        <v>2.252962920179158</v>
+        <v>2.279295890521549</v>
       </c>
       <c r="N6" t="n">
-        <v>9.375182305552153</v>
+        <v>9.542140539554754</v>
       </c>
       <c r="O6" t="n">
-        <v>3.061891948706249</v>
+        <v>3.089035535495627</v>
       </c>
       <c r="P6" t="n">
-        <v>365.2669704737131</v>
+        <v>365.3477114257325</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30523,28 +30707,28 @@
         <v>0.1145</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02241542313772934</v>
+        <v>0.01939436974783402</v>
       </c>
       <c r="J7" t="n">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="K7" t="n">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002187480296413247</v>
+        <v>0.001656377414984145</v>
       </c>
       <c r="M7" t="n">
-        <v>2.611830452290919</v>
+        <v>2.610195345178801</v>
       </c>
       <c r="N7" t="n">
-        <v>12.7050129658673</v>
+        <v>12.66552277132182</v>
       </c>
       <c r="O7" t="n">
-        <v>3.564409202920913</v>
+        <v>3.558865376959603</v>
       </c>
       <c r="P7" t="n">
-        <v>365.9802920529215</v>
+        <v>366.0127076866</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30601,28 +30785,28 @@
         <v>0.105</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.02907920234351079</v>
+        <v>-0.0318921107309593</v>
       </c>
       <c r="J8" t="n">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="K8" t="n">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002652843831293161</v>
+        <v>0.003228202043647044</v>
       </c>
       <c r="M8" t="n">
-        <v>3.205022607408297</v>
+        <v>3.198581049318959</v>
       </c>
       <c r="N8" t="n">
-        <v>17.62284732315338</v>
+        <v>17.54496840592595</v>
       </c>
       <c r="O8" t="n">
-        <v>4.197957518026281</v>
+        <v>4.188671436855122</v>
       </c>
       <c r="P8" t="n">
-        <v>369.6967590745633</v>
+        <v>369.7269362385522</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30679,28 +30863,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02250493836160353</v>
+        <v>0.02054052802570763</v>
       </c>
       <c r="J9" t="n">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="K9" t="n">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001364256606051772</v>
+        <v>0.001151903790273079</v>
       </c>
       <c r="M9" t="n">
-        <v>3.381285124180285</v>
+        <v>3.369267619322653</v>
       </c>
       <c r="N9" t="n">
-        <v>20.55148115684107</v>
+        <v>20.43889799673128</v>
       </c>
       <c r="O9" t="n">
-        <v>4.533374147016885</v>
+        <v>4.520939946154038</v>
       </c>
       <c r="P9" t="n">
-        <v>368.9950319141713</v>
+        <v>369.0161033300498</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30738,7 +30922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J639"/>
+  <dimension ref="A1:J643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63905,7 +64089,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>-36.49448071315832,174.74286899529133</t>
+          <t>-36.49447693572117,174.742864683364</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -63944,6 +64128,214 @@
         </is>
       </c>
       <c r="J639" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>-36.49445970530399,174.7428450149288</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>-36.49500566219274,174.7422490557146</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>-36.49552078674862,174.7416034606322</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>-36.49608255183433,174.74102103161235</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>-36.49671933787974,174.74056864628963</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>-36.49740049636789,174.74027905282412</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>-36.498089045670206,174.7400510215481</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>-36.49880088601504,174.73993781562586</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>-36.49442438293774,174.74280469466407</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>-36.495006258632365,174.7422497365472</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>-36.49552688952603,174.74161136833703</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>-36.4960830612111,174.74102181342602</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>-36.496719023848236,174.74056796859827</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>-36.49739882667526,174.74027291770085</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>-36.49808945310928,174.7400535388786</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>-36.4988008281117,174.73993726211398</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>-36.49442438293774,174.74280469466407</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>-36.49500844557762,174.74225223293334</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>-36.495523900410646,174.74160749517534</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>-36.49608023134008,174.74101747001686</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>-36.49671426851351,174.74055770641564</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>-36.49739494032049,174.7402586376735</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>-36.49808794735588,174.74004423570076</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>-36.4988008281117,174.73993726211398</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>-36.49441232163854,174.7427909267772</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>-36.495002679994556,174.74224565155194</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>-36.49552016401621,174.74160265372362</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>-36.49608113689882,174.74101885990774</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>-36.49671727424405,174.74056419288942</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>-36.4973960918332,174.74026286879257</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>-36.49808860280156,174.74004828531932</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>-36.49880131449972,174.73994191161376</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0129/nzd0129.xlsx
+++ b/data/nzd0129/nzd0129.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J643"/>
+  <dimension ref="A1:J647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23580,6 +23580,150 @@
         <v>368.32</v>
       </c>
       <c r="J643" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>324.86</v>
+      </c>
+      <c r="C644" t="n">
+        <v>340.91</v>
+      </c>
+      <c r="D644" t="n">
+        <v>345.44</v>
+      </c>
+      <c r="E644" t="n">
+        <v>346.41</v>
+      </c>
+      <c r="F644" t="n">
+        <v>359.45</v>
+      </c>
+      <c r="G644" t="n">
+        <v>364.32</v>
+      </c>
+      <c r="H644" t="n">
+        <v>366.74</v>
+      </c>
+      <c r="I644" t="n">
+        <v>368.3</v>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>324.18</v>
+      </c>
+      <c r="C645" t="n">
+        <v>341.06</v>
+      </c>
+      <c r="D645" t="n">
+        <v>345.58</v>
+      </c>
+      <c r="E645" t="n">
+        <v>346.9</v>
+      </c>
+      <c r="F645" t="n">
+        <v>360.38</v>
+      </c>
+      <c r="G645" t="n">
+        <v>364.86</v>
+      </c>
+      <c r="H645" t="n">
+        <v>367.47</v>
+      </c>
+      <c r="I645" t="n">
+        <v>368.71</v>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>321.28</v>
+      </c>
+      <c r="C646" t="n">
+        <v>339.5</v>
+      </c>
+      <c r="D646" t="n">
+        <v>345.2</v>
+      </c>
+      <c r="E646" t="n">
+        <v>346.75</v>
+      </c>
+      <c r="F646" t="n">
+        <v>360.23</v>
+      </c>
+      <c r="G646" t="n">
+        <v>365.22</v>
+      </c>
+      <c r="H646" t="n">
+        <v>368.25</v>
+      </c>
+      <c r="I646" t="n">
+        <v>368.91</v>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>319.95</v>
+      </c>
+      <c r="C647" t="n">
+        <v>338.79</v>
+      </c>
+      <c r="D647" t="n">
+        <v>345.03</v>
+      </c>
+      <c r="E647" t="n">
+        <v>346</v>
+      </c>
+      <c r="F647" t="n">
+        <v>359.83</v>
+      </c>
+      <c r="G647" t="n">
+        <v>364.53</v>
+      </c>
+      <c r="H647" t="n">
+        <v>368.34</v>
+      </c>
+      <c r="I647" t="n">
+        <v>368.72</v>
+      </c>
+      <c r="J647" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23596,7 +23740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B655"/>
+  <dimension ref="A1:B659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30149,6 +30293,46 @@
       </c>
       <c r="B655" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -30317,28 +30501,28 @@
         <v>0.059</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2927933749273703</v>
+        <v>-0.3197385012563244</v>
       </c>
       <c r="J2" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="K2" t="n">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03315631136190123</v>
+        <v>0.03901712627786569</v>
       </c>
       <c r="M2" t="n">
-        <v>10.40272735325131</v>
+        <v>10.48271660383779</v>
       </c>
       <c r="N2" t="n">
-        <v>140.1949020948929</v>
+        <v>142.2894698389242</v>
       </c>
       <c r="O2" t="n">
-        <v>11.84039281843694</v>
+        <v>11.92851498883764</v>
       </c>
       <c r="P2" t="n">
-        <v>352.4267959557174</v>
+        <v>352.7166466764454</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30395,28 +30579,28 @@
         <v>0.0418</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3936199376762383</v>
+        <v>-0.4020981764300834</v>
       </c>
       <c r="J3" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="K3" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L3" t="n">
-        <v>0.144501661037819</v>
+        <v>0.150883341426434</v>
       </c>
       <c r="M3" t="n">
-        <v>6.068891830517907</v>
+        <v>6.079590506000256</v>
       </c>
       <c r="N3" t="n">
-        <v>51.31033680225099</v>
+        <v>51.28769950020581</v>
       </c>
       <c r="O3" t="n">
-        <v>7.163123397111835</v>
+        <v>7.161543094906698</v>
       </c>
       <c r="P3" t="n">
-        <v>357.5864670630987</v>
+        <v>357.6777352856223</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30473,28 +30657,28 @@
         <v>0.0655</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1640083304711157</v>
+        <v>-0.1713622150764641</v>
       </c>
       <c r="J4" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="K4" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07150680558206102</v>
+        <v>0.07774556825185508</v>
       </c>
       <c r="M4" t="n">
-        <v>3.364878627948316</v>
+        <v>3.381077507495658</v>
       </c>
       <c r="N4" t="n">
-        <v>19.53743384835627</v>
+        <v>19.63487711480879</v>
       </c>
       <c r="O4" t="n">
-        <v>4.420116949624328</v>
+        <v>4.431125942106452</v>
       </c>
       <c r="P4" t="n">
-        <v>355.7286729560913</v>
+        <v>355.8078276762159</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30551,28 +30735,28 @@
         <v>0.061</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3025526375742647</v>
+        <v>-0.308031127523143</v>
       </c>
       <c r="J5" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="K5" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2627124357098071</v>
+        <v>0.2707836633847303</v>
       </c>
       <c r="M5" t="n">
-        <v>2.824367913248808</v>
+        <v>2.833356232683402</v>
       </c>
       <c r="N5" t="n">
-        <v>14.35189322577166</v>
+        <v>14.38469364270875</v>
       </c>
       <c r="O5" t="n">
-        <v>3.788389265343737</v>
+        <v>3.792715866329661</v>
       </c>
       <c r="P5" t="n">
-        <v>359.1405497263555</v>
+        <v>359.1995386993489</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30629,28 +30813,28 @@
         <v>0.0892</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.006974324035298916</v>
+        <v>-0.01333843111312814</v>
       </c>
       <c r="J6" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="K6" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002846989093194807</v>
+        <v>0.001037143763677362</v>
       </c>
       <c r="M6" t="n">
-        <v>2.279295890521549</v>
+        <v>2.29927867816194</v>
       </c>
       <c r="N6" t="n">
-        <v>9.542140539554754</v>
+        <v>9.647112792601636</v>
       </c>
       <c r="O6" t="n">
-        <v>3.089035535495627</v>
+        <v>3.105980166163596</v>
       </c>
       <c r="P6" t="n">
-        <v>365.3477114257325</v>
+        <v>365.4162321292</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30707,28 +30891,28 @@
         <v>0.1145</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01939436974783402</v>
+        <v>0.01718287942798584</v>
       </c>
       <c r="J7" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="K7" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001656377414984145</v>
+        <v>0.001316639652834239</v>
       </c>
       <c r="M7" t="n">
-        <v>2.610195345178801</v>
+        <v>2.604677970561626</v>
       </c>
       <c r="N7" t="n">
-        <v>12.66552277132182</v>
+        <v>12.607536799616</v>
       </c>
       <c r="O7" t="n">
-        <v>3.558865376959603</v>
+        <v>3.550709337529052</v>
       </c>
       <c r="P7" t="n">
-        <v>366.0127076866</v>
+        <v>366.0365173250049</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30785,28 +30969,28 @@
         <v>0.105</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0318921107309593</v>
+        <v>-0.03331766033597826</v>
       </c>
       <c r="J8" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="K8" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003228202043647044</v>
+        <v>0.003569018526937029</v>
       </c>
       <c r="M8" t="n">
-        <v>3.198581049318959</v>
+        <v>3.185583595423949</v>
       </c>
       <c r="N8" t="n">
-        <v>17.54496840592595</v>
+        <v>17.44716580880674</v>
       </c>
       <c r="O8" t="n">
-        <v>4.188671436855122</v>
+        <v>4.176980465456684</v>
       </c>
       <c r="P8" t="n">
-        <v>369.7269362385522</v>
+        <v>369.7422754945266</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30863,28 +31047,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02054052802570763</v>
+        <v>0.01942337298904604</v>
       </c>
       <c r="J9" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="K9" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001151903790273079</v>
+        <v>0.00104423673418319</v>
       </c>
       <c r="M9" t="n">
-        <v>3.369267619322653</v>
+        <v>3.353478034360643</v>
       </c>
       <c r="N9" t="n">
-        <v>20.43889799673128</v>
+        <v>20.31767765444572</v>
       </c>
       <c r="O9" t="n">
-        <v>4.520939946154038</v>
+        <v>4.507513466917844</v>
       </c>
       <c r="P9" t="n">
-        <v>369.0161033300498</v>
+        <v>369.0281294338564</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30922,7 +31106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J643"/>
+  <dimension ref="A1:J647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64341,6 +64525,214 @@
         </is>
       </c>
     </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>-36.494412454180306,174.74279107807263</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>-36.495001553386324,174.742244365535</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>-36.49551985265,174.74160225026932</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>-36.49607870320965,174.74101512457605</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>-36.496718485508495,174.74056680684168</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>-36.49739807819226,174.74027016747326</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>-36.498088921666984,174.74005025540404</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>-36.49880129133838,174.739941690209</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>-36.4944079477604,174.74278593402806</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>-36.495002547452415,174.74224550025582</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>-36.49552072447539,174.74160337994135</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>-36.49608147648335,174.74101938111684</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>-36.496722657641136,174.74057581045565</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>-36.49739963273382,174.74027587948444</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>-36.49809021484308,174.74005824519224</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>-36.49880176614557,174.73994622900645</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>-36.494388729202186,174.74276399619768</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>-36.49499220916454,174.7422336991606</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>-36.49551835809216,174.7416003136888</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>-36.49608062752203,174.74101807809413</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>-36.49672198471657,174.74057435825978</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>-36.497400669094695,174.74027968749203</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>-36.498091596592275,174.74006678222645</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>-36.49880199775875,174.739948443054</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>-36.49437991517228,174.7427539350584</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>-36.49498750391773,174.74222832815033</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>-36.495517299447,174.74159894194426</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>-36.4960763827152,174.74101156298093</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>-36.49672019025095,174.7405704857376</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>-36.497398682736225,174.7402723888109</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>-36.498091756024834,174.7400677672689</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>-36.49880177772623,174.73994633970884</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0129/nzd0129.xlsx
+++ b/data/nzd0129/nzd0129.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J647"/>
+  <dimension ref="A1:J649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23724,6 +23724,78 @@
         <v>368.72</v>
       </c>
       <c r="J647" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>319.79</v>
+      </c>
+      <c r="C648" t="n">
+        <v>338.89</v>
+      </c>
+      <c r="D648" t="n">
+        <v>345.68</v>
+      </c>
+      <c r="E648" t="n">
+        <v>346.31</v>
+      </c>
+      <c r="F648" t="n">
+        <v>360.35</v>
+      </c>
+      <c r="G648" t="n">
+        <v>365.25</v>
+      </c>
+      <c r="H648" t="n">
+        <v>369.54</v>
+      </c>
+      <c r="I648" t="n">
+        <v>369.31</v>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>321.71</v>
+      </c>
+      <c r="C649" t="n">
+        <v>340.01</v>
+      </c>
+      <c r="D649" t="n">
+        <v>346.32</v>
+      </c>
+      <c r="E649" t="n">
+        <v>347.14</v>
+      </c>
+      <c r="F649" t="n">
+        <v>361.02</v>
+      </c>
+      <c r="G649" t="n">
+        <v>366.03</v>
+      </c>
+      <c r="H649" t="n">
+        <v>369.87</v>
+      </c>
+      <c r="I649" t="n">
+        <v>369.73</v>
+      </c>
+      <c r="J649" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23740,7 +23812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B659"/>
+  <dimension ref="A1:B661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30333,6 +30405,26 @@
       </c>
       <c r="B659" t="n">
         <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="n">
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>
@@ -30501,28 +30593,28 @@
         <v>0.059</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3197385012563244</v>
+        <v>-0.3339995161579384</v>
       </c>
       <c r="J2" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="K2" t="n">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03901712627786569</v>
+        <v>0.0422284962913726</v>
       </c>
       <c r="M2" t="n">
-        <v>10.48271660383779</v>
+        <v>10.52642110156547</v>
       </c>
       <c r="N2" t="n">
-        <v>142.2894698389242</v>
+        <v>143.5202460296754</v>
       </c>
       <c r="O2" t="n">
-        <v>11.92851498883764</v>
+        <v>11.97999357385785</v>
       </c>
       <c r="P2" t="n">
-        <v>352.7166466764454</v>
+        <v>352.8705654639168</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30579,28 +30671,28 @@
         <v>0.0418</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4020981764300834</v>
+        <v>-0.4065967282260697</v>
       </c>
       <c r="J3" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="K3" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="L3" t="n">
-        <v>0.150883341426434</v>
+        <v>0.1542313461854996</v>
       </c>
       <c r="M3" t="n">
-        <v>6.079590506000256</v>
+        <v>6.086238011273918</v>
       </c>
       <c r="N3" t="n">
-        <v>51.28769950020581</v>
+        <v>51.29560282744854</v>
       </c>
       <c r="O3" t="n">
-        <v>7.161543094906698</v>
+        <v>7.162094863058472</v>
       </c>
       <c r="P3" t="n">
-        <v>357.6777352856223</v>
+        <v>357.7263202822997</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30657,28 +30749,28 @@
         <v>0.0655</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1713622150764641</v>
+        <v>-0.1745269650408287</v>
       </c>
       <c r="J4" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="K4" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07774556825185508</v>
+        <v>0.08061095156441123</v>
       </c>
       <c r="M4" t="n">
-        <v>3.381077507495658</v>
+        <v>3.386777165611954</v>
       </c>
       <c r="N4" t="n">
-        <v>19.63487711480879</v>
+        <v>19.65639153952359</v>
       </c>
       <c r="O4" t="n">
-        <v>4.431125942106452</v>
+        <v>4.433552925084304</v>
       </c>
       <c r="P4" t="n">
-        <v>355.8078276762159</v>
+        <v>355.8420074524773</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30735,28 +30827,28 @@
         <v>0.061</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.308031127523143</v>
+        <v>-0.310564602560072</v>
       </c>
       <c r="J5" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="K5" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2707836633847303</v>
+        <v>0.2746710227917927</v>
       </c>
       <c r="M5" t="n">
-        <v>2.833356232683402</v>
+        <v>2.836987263063173</v>
       </c>
       <c r="N5" t="n">
-        <v>14.38469364270875</v>
+        <v>14.39322026471902</v>
       </c>
       <c r="O5" t="n">
-        <v>3.792715866329661</v>
+        <v>3.793839778472335</v>
       </c>
       <c r="P5" t="n">
-        <v>359.1995386993489</v>
+        <v>359.2269094066609</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30813,28 +30905,28 @@
         <v>0.0892</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01333843111312814</v>
+        <v>-0.01601418107007591</v>
       </c>
       <c r="J6" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="K6" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001037143763677362</v>
+        <v>0.001495513366930989</v>
       </c>
       <c r="M6" t="n">
-        <v>2.29927867816194</v>
+        <v>2.306863269027543</v>
       </c>
       <c r="N6" t="n">
-        <v>9.647112792601636</v>
+        <v>9.67611609729901</v>
       </c>
       <c r="O6" t="n">
-        <v>3.105980166163596</v>
+        <v>3.110645607795753</v>
       </c>
       <c r="P6" t="n">
-        <v>365.4162321292</v>
+        <v>365.4451399612727</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30891,28 +30983,28 @@
         <v>0.1145</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01718287942798584</v>
+        <v>0.01665718391013667</v>
       </c>
       <c r="J7" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="K7" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001316639652834239</v>
+        <v>0.001245695368361388</v>
       </c>
       <c r="M7" t="n">
-        <v>2.604677970561626</v>
+        <v>2.599143908042596</v>
       </c>
       <c r="N7" t="n">
-        <v>12.607536799616</v>
+        <v>12.57134819875743</v>
       </c>
       <c r="O7" t="n">
-        <v>3.550709337529052</v>
+        <v>3.545609707618343</v>
       </c>
       <c r="P7" t="n">
-        <v>366.0365173250049</v>
+        <v>366.0421966267232</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30969,28 +31061,28 @@
         <v>0.105</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.03331766033597826</v>
+        <v>-0.03278930265731963</v>
       </c>
       <c r="J8" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="K8" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003569018526937029</v>
+        <v>0.003480491989849344</v>
       </c>
       <c r="M8" t="n">
-        <v>3.185583595423949</v>
+        <v>3.178529346082088</v>
       </c>
       <c r="N8" t="n">
-        <v>17.44716580880674</v>
+        <v>17.39567987143458</v>
       </c>
       <c r="O8" t="n">
-        <v>4.176980465456684</v>
+        <v>4.170812855000159</v>
       </c>
       <c r="P8" t="n">
-        <v>369.7422754945266</v>
+        <v>369.7365672221683</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31047,28 +31139,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01942337298904604</v>
+        <v>0.01940180474867269</v>
       </c>
       <c r="J9" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="K9" t="n">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00104423673418319</v>
+        <v>0.001049121274153464</v>
       </c>
       <c r="M9" t="n">
-        <v>3.353478034360643</v>
+        <v>3.343765121142396</v>
       </c>
       <c r="N9" t="n">
-        <v>20.31767765444572</v>
+        <v>20.25510871498241</v>
       </c>
       <c r="O9" t="n">
-        <v>4.507513466917844</v>
+        <v>4.500567599201506</v>
       </c>
       <c r="P9" t="n">
-        <v>369.0281294338564</v>
+        <v>369.0283623711198</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31106,7 +31198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J647"/>
+  <dimension ref="A1:J649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64733,6 +64825,110 @@
         </is>
       </c>
     </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>-36.49437885483781,174.74275272469595</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>-36.49498816662857,174.74222908463062</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>-36.495521347207806,174.74160418684994</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>-36.496078137235415,174.74101425589427</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>-36.49672252305623,174.7405755200165</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>-36.497400755458095,174.740280004826</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>-36.4980938817915,174.74008090116828</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>-36.498802460985026,174.73995287114914</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>-36.494391578850745,174.74276724904772</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>-36.49499558898956,174.74223755721061</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>-36.495525332695124,174.74160935106528</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>-36.49608283482142,174.74102146595325</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>-36.49672552878576,174.74058200649165</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>-36.497403000906225,174.74028825550945</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>-36.498094466377076,174.74008451299073</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>-36.49880294737243,174.73995752064909</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
